--- a/final_data_pipeline/output/311314longform.xlsx
+++ b/final_data_pipeline/output/311314longform.xlsx
@@ -807,7 +807,7 @@
         <v>77</v>
       </c>
       <c r="AA2">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB2">
         <v>8000</v>
@@ -890,7 +890,7 @@
         <v>77</v>
       </c>
       <c r="AA3">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB3">
         <v>8000</v>
@@ -979,7 +979,7 @@
         <v>77</v>
       </c>
       <c r="AA4">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB4">
         <v>8000</v>
@@ -1068,7 +1068,7 @@
         <v>77</v>
       </c>
       <c r="AA5">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB5">
         <v>8000</v>
@@ -1151,7 +1151,7 @@
         <v>77</v>
       </c>
       <c r="AA6">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB6">
         <v>8000</v>
@@ -1234,7 +1234,7 @@
         <v>77</v>
       </c>
       <c r="AA7">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB7">
         <v>8000</v>
@@ -1317,7 +1317,7 @@
         <v>77</v>
       </c>
       <c r="AA8">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB8">
         <v>8000</v>
@@ -1406,7 +1406,7 @@
         <v>77</v>
       </c>
       <c r="AA9">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB9">
         <v>8000</v>
@@ -1489,7 +1489,7 @@
         <v>77</v>
       </c>
       <c r="AA10">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB10">
         <v>8000</v>
@@ -1578,7 +1578,7 @@
         <v>77</v>
       </c>
       <c r="AA11">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB11">
         <v>8000</v>
@@ -1661,7 +1661,7 @@
         <v>77</v>
       </c>
       <c r="AA12">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB12">
         <v>8000</v>
@@ -1744,7 +1744,7 @@
         <v>77</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB13">
         <v>8000</v>
@@ -1827,7 +1827,7 @@
         <v>77</v>
       </c>
       <c r="AA14">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB14">
         <v>8000</v>
@@ -1910,7 +1910,7 @@
         <v>77</v>
       </c>
       <c r="AA15">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB15">
         <v>8000</v>
@@ -1999,7 +1999,7 @@
         <v>77</v>
       </c>
       <c r="AA16">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB16">
         <v>8000</v>
@@ -2088,7 +2088,7 @@
         <v>77</v>
       </c>
       <c r="AA17">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB17">
         <v>8000</v>
@@ -2171,7 +2171,7 @@
         <v>77</v>
       </c>
       <c r="AA18">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB18">
         <v>8000</v>
@@ -2254,7 +2254,7 @@
         <v>77</v>
       </c>
       <c r="AA19">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB19">
         <v>8000</v>
@@ -2337,7 +2337,7 @@
         <v>77</v>
       </c>
       <c r="AA20">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB20">
         <v>8000</v>
@@ -2426,7 +2426,7 @@
         <v>77</v>
       </c>
       <c r="AA21">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB21">
         <v>8000</v>
@@ -2515,7 +2515,7 @@
         <v>77</v>
       </c>
       <c r="AA22">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB22">
         <v>8000</v>
@@ -2598,7 +2598,7 @@
         <v>77</v>
       </c>
       <c r="AA23">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB23">
         <v>8000</v>
@@ -2681,7 +2681,7 @@
         <v>77</v>
       </c>
       <c r="AA24">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB24">
         <v>8000</v>
@@ -2764,7 +2764,7 @@
         <v>77</v>
       </c>
       <c r="AA25">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AB25">
         <v>8000</v>
@@ -2847,7 +2847,7 @@
         <v>77</v>
       </c>
       <c r="AA26">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="AB26">
         <v>8000</v>
@@ -2930,7 +2930,7 @@
         <v>77</v>
       </c>
       <c r="AA27">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="AB27">
         <v>8000</v>
@@ -3013,7 +3013,7 @@
         <v>77</v>
       </c>
       <c r="AA28">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="AB28">
         <v>8000</v>
@@ -3096,7 +3096,7 @@
         <v>77</v>
       </c>
       <c r="AA29">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="AB29">
         <v>8000</v>
@@ -3179,7 +3179,7 @@
         <v>77</v>
       </c>
       <c r="AA30">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="AB30">
         <v>8000</v>
@@ -3262,7 +3262,7 @@
         <v>77</v>
       </c>
       <c r="AA31">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="AB31">
         <v>8000</v>
@@ -3345,7 +3345,7 @@
         <v>77</v>
       </c>
       <c r="AA32">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="AB32">
         <v>8000</v>
@@ -3428,7 +3428,7 @@
         <v>77</v>
       </c>
       <c r="AA33">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="AB33">
         <v>8000</v>
@@ -3511,7 +3511,7 @@
         <v>77</v>
       </c>
       <c r="AA34">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="AB34">
         <v>8000</v>
@@ -3594,7 +3594,7 @@
         <v>77</v>
       </c>
       <c r="AA35">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="AB35">
         <v>8000</v>
@@ -3677,7 +3677,7 @@
         <v>77</v>
       </c>
       <c r="AA36">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="AB36">
         <v>8000</v>
@@ -3760,7 +3760,7 @@
         <v>77</v>
       </c>
       <c r="AA37">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="AB37">
         <v>8000</v>
@@ -3843,7 +3843,7 @@
         <v>77</v>
       </c>
       <c r="AA38">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="AB38">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         <v>77</v>
       </c>
       <c r="AA39">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="AB39">
         <v>8000</v>
@@ -4009,7 +4009,7 @@
         <v>77</v>
       </c>
       <c r="AA40">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="AB40">
         <v>8000</v>
@@ -4092,7 +4092,7 @@
         <v>77</v>
       </c>
       <c r="AA41">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="AB41">
         <v>8000</v>
@@ -4181,7 +4181,7 @@
         <v>77</v>
       </c>
       <c r="AA42">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB42">
         <v>8000</v>
@@ -4264,7 +4264,7 @@
         <v>77</v>
       </c>
       <c r="AA43">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB43">
         <v>8000</v>
@@ -4347,7 +4347,7 @@
         <v>77</v>
       </c>
       <c r="AA44">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB44">
         <v>8000</v>
@@ -4436,7 +4436,7 @@
         <v>77</v>
       </c>
       <c r="AA45">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB45">
         <v>8000</v>
@@ -4519,7 +4519,7 @@
         <v>77</v>
       </c>
       <c r="AA46">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB46">
         <v>8000</v>
@@ -4608,7 +4608,7 @@
         <v>77</v>
       </c>
       <c r="AA47">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB47">
         <v>8000</v>
@@ -4697,7 +4697,7 @@
         <v>77</v>
       </c>
       <c r="AA48">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB48">
         <v>8000</v>
@@ -4786,7 +4786,7 @@
         <v>77</v>
       </c>
       <c r="AA49">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB49">
         <v>8000</v>
@@ -4875,7 +4875,7 @@
         <v>77</v>
       </c>
       <c r="AA50">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB50">
         <v>8000</v>
@@ -4958,7 +4958,7 @@
         <v>77</v>
       </c>
       <c r="AA51">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB51">
         <v>8000</v>
@@ -5047,7 +5047,7 @@
         <v>77</v>
       </c>
       <c r="AA52">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB52">
         <v>8000</v>
@@ -5136,7 +5136,7 @@
         <v>77</v>
       </c>
       <c r="AA53">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB53">
         <v>8000</v>
@@ -5219,7 +5219,7 @@
         <v>77</v>
       </c>
       <c r="AA54">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB54">
         <v>8000</v>
@@ -5308,7 +5308,7 @@
         <v>77</v>
       </c>
       <c r="AA55">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB55">
         <v>8000</v>
@@ -5397,7 +5397,7 @@
         <v>77</v>
       </c>
       <c r="AA56">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB56">
         <v>8000</v>
@@ -5486,7 +5486,7 @@
         <v>77</v>
       </c>
       <c r="AA57">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB57">
         <v>8000</v>
@@ -5575,7 +5575,7 @@
         <v>77</v>
       </c>
       <c r="AA58">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB58">
         <v>8000</v>
@@ -5664,7 +5664,7 @@
         <v>77</v>
       </c>
       <c r="AA59">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB59">
         <v>8000</v>
@@ -5747,7 +5747,7 @@
         <v>77</v>
       </c>
       <c r="AA60">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB60">
         <v>8000</v>
@@ -5836,7 +5836,7 @@
         <v>77</v>
       </c>
       <c r="AA61">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB61">
         <v>8000</v>
@@ -5919,7 +5919,7 @@
         <v>77</v>
       </c>
       <c r="AA62">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB62">
         <v>8000</v>
@@ -6002,7 +6002,7 @@
         <v>77</v>
       </c>
       <c r="AA63">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB63">
         <v>8000</v>
@@ -6091,7 +6091,7 @@
         <v>77</v>
       </c>
       <c r="AA64">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB64">
         <v>8000</v>
@@ -6180,7 +6180,7 @@
         <v>77</v>
       </c>
       <c r="AA65">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB65">
         <v>8000</v>
